--- a/docs/AI_Job_Displacement_LLM_Framework.xlsx
+++ b/docs/AI_Job_Displacement_LLM_Framework.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Temperature</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3</t>
+    <t xml:space="preserve">0.2</t>
   </si>
   <si>
     <t xml:space="preserve">Lower temperature ensures higher consistency, reducing variance across multiple evaluations of the same job.</t>
@@ -312,27 +312,7 @@
     <t xml:space="preserve">Write, update, and maintain computer programs or software packages to handle specific jobs such as tracking inventory, storing or retrieving data, or controlling other equipment.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="16"/>
-        <color rgb="FF1F4E78"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Expected LLM Output </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="16"/>
-        <color rgb="FF1F4E78"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">(Example for Software Developer Task)</t>
-    </r>
+    <t xml:space="preserve">Expected LLM Output (Example for Software Developer Task)</t>
   </si>
   <si>
     <t xml:space="preserve">Task Analyzed: 'Write, update, and maintain computer programs or software packages...'</t>
@@ -378,7 +358,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0%"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -444,13 +424,6 @@
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="16"/>
-      <color rgb="FF1F4E78"/>
-      <name val="Cambria"/>
-      <family val="0"/>
     </font>
     <font>
       <b val="true"/>
@@ -549,64 +522,68 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -881,94 +858,94 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="80"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="80"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -994,229 +971,229 @@
   <dimension ref="A1:I12"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="7" t="n">
         <v>0.15</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="G6" s="8" t="n">
         <v>0.15</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="7" t="n">
         <v>0.15</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="G8" s="8" t="n">
         <v>0.15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G9" s="7" t="n">
         <v>0.15</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G10" s="8" t="n">
         <v>0.15</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="7" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="10" t="n">
         <f aca="false">SUM(G5:G11)</f>
         <v>1</v>
       </c>
@@ -1252,384 +1229,384 @@
   <dimension ref="A1:H42"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="4" style="1" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="11" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
+      <c r="A11" s="12"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
+      <c r="A13" s="12"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="11"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="11"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="11"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="11"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
+      <c r="A33" s="12"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
+      <c r="A34" s="12"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
+      <c r="A35" s="12"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
     </row>
     <row r="38" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="3" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="5" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="36.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="4" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1657,388 +1634,388 @@
   <dimension ref="A1:H40"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="1" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="1" style="1" width="20"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="20.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="20.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="A8" s="15"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
+      <c r="A12" s="15"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
+      <c r="A14" s="15"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
+      <c r="A20" s="15"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="A24" s="15"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="14"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
+      <c r="A25" s="15"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
+      <c r="A26" s="15"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="14"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="14"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="14"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="14"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
+      <c r="A30" s="15"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="14"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
+      <c r="A31" s="15"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="14"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
+      <c r="A32" s="15"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="14"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
+      <c r="A33" s="15"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="14"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
+      <c r="A34" s="15"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="14"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
+      <c r="A35" s="15"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="14"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
+      <c r="A36" s="15"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="14"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
+      <c r="A37" s="15"/>
+      <c r="B37" s="15"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="14"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
+      <c r="A38" s="15"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="14"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
+      <c r="A39" s="15"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="14"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
+      <c r="A40" s="15"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/docs/AI_Job_Displacement_LLM_Framework.xlsx
+++ b/docs/AI_Job_Displacement_LLM_Framework.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="System Config" sheetId="1" state="visible" r:id="rId3"/>
@@ -103,7 +103,7 @@
     <t xml:space="preserve">JSON Key</t>
   </si>
   <si>
-    <t xml:space="preserve">What it Measures (The Isolated Variable)</t>
+    <t xml:space="preserve">What it Measures</t>
   </si>
   <si>
     <t xml:space="preserve">Prompt Question</t>
@@ -1637,7 +1637,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="1" style="1" width="20"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="20.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>87</v>
       </c>
